--- a/s01/S01_ALU_02_Instrumento_Expediente.xlsx
+++ b/s01/S01_ALU_02_Instrumento_Expediente.xlsx
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">Tu cliente califica como de riesgo bajo, o como de riesgo medio</t>
   </si>
   <si>
-    <t xml:space="preserve">Bajo riesgo: medidas simplificadas, con la obligación de solicitar los documentos en original o copia certificada por fedatario. Riesgo medio: régimen propio del 17 Bis. Y si el cliente se aparta de los criterios de bajo riesgo, integras el expediente completo.</t>
+    <t xml:space="preserve">Bajo riesgo: medidas simplificadas del RCG 17, con la obligación de solicitar los documentos en original o copia certificada por fedatario, y sólo si además tu entidad quedó en bajo riesgo conforme al Art. 15 del Reglamento: son dos condiciones acumulativas. Riesgo medio: régimen propio del 17 Bis. Y si el cliente se aparta de los criterios de bajo riesgo, integras el expediente completo.</t>
   </si>
   <si>
     <t xml:space="preserve">RCG 17 y 17 Bis</t>
